--- a/src/beastmistress/assets/data/skills.xlsx
+++ b/src/beastmistress/assets/data/skills.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="44">
   <si>
     <t>Description</t>
   </si>
@@ -33,9 +33,6 @@
     <t>Recharge</t>
   </si>
   <si>
-    <t>Weather</t>
-  </si>
-  <si>
     <t>Sunshine</t>
   </si>
   <si>
@@ -117,12 +114,6 @@
     <t>Natural Healing</t>
   </si>
   <si>
-    <t>Heals the user for _A life.</t>
-  </si>
-  <si>
-    <t>Defensive</t>
-  </si>
-  <si>
     <t>Damage</t>
   </si>
   <si>
@@ -142,6 +133,21 @@
   </si>
   <si>
     <t>Water</t>
+  </si>
+  <si>
+    <t>Wait</t>
+  </si>
+  <si>
+    <t>Wait.</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Heal target allied beast for _A life.</t>
   </si>
 </sst>
 </file>
@@ -507,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
@@ -528,10 +534,10 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -543,90 +549,90 @@
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="L1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="4">
         <v>0.33</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M2" s="2">
         <v>0</v>
@@ -635,63 +641,63 @@
         <v>4</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="G3" s="2">
         <v>30</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M3" s="2">
         <v>0</v>
@@ -700,63 +706,63 @@
         <v>0</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2">
         <v>50</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M4" s="2">
         <v>0</v>
@@ -765,63 +771,63 @@
         <v>5</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="G5" s="2">
         <v>30</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M5" s="2">
         <v>0</v>
@@ -830,25 +836,90 @@
         <v>0</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
